--- a/outputs/evaluation/architecture/validation/gemini-3-5/CF_M05/run_3/CF_M05_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/gemini-3-5/CF_M05/run_3/CF_M05_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.7073</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.4915</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.7941</v>
       </c>
       <c r="D3" t="n">
+        <v>0.5294</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9472</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.2857</v>
       </c>
       <c r="D4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.8208</v>
       </c>
     </row>
@@ -1199,7 +1213,6 @@
       <c r="D2" t="n">
         <v>0.7506</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1220,7 +1233,6 @@
           <t>['AU_16', 'AU_18']</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_71</t>
@@ -1231,7 +1243,6 @@
           <t>portal, access control</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1250,7 +1261,6 @@
           <t>CF_M05_AU01, CF_M05_AU02, CF_M05_AU03, CF_M05_AU04, CF_M05_AU05, CF_M05_AU11, CF_M05_AU12</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M05_AU22</t>
@@ -1301,14 +1311,11 @@
           <t>69</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_36</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Contract Layer (DTO/Mappers)</t>
@@ -1333,13 +1340,11 @@
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M05_AU20</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1380,14 +1385,11 @@
           <t>57</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_16</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Portal Microservice</t>
@@ -1414,13 +1416,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M05_AU02</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1461,14 +1461,11 @@
           <t>57</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_15</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Leader Microservice</t>
@@ -1494,13 +1491,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M05_AU01</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1541,14 +1536,11 @@
           <t>59</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_20</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Scheduler Microservice</t>
@@ -1577,13 +1569,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M05_AU05</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1624,14 +1614,11 @@
           <t>58</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_19</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Communication Log Microservice</t>
@@ -1660,13 +1647,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M05_AU04</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1707,14 +1692,11 @@
           <t>58</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_18</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Access Control Microservice</t>
@@ -1739,13 +1721,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M05_AU03</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1766,7 +1746,6 @@
       <c r="D9" t="n">
         <v>0.891</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1787,7 +1766,6 @@
           <t>['AU_45', 'AU_34']</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_69</t>
@@ -1798,7 +1776,6 @@
           <t>spring data, data access layer</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1817,7 +1794,6 @@
           <t>CF_M05_AU21, CF_M05_AU16</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M05_AU26</t>
@@ -1868,14 +1844,11 @@
           <t>68</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_32</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Presentation Layer (Controllers)</t>
@@ -1901,13 +1874,11 @@
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M05_AU17</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1948,14 +1919,11 @@
           <t>69</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_34</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Data access layer (Repositories)</t>
@@ -1979,13 +1947,11 @@
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M05_AU21</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2026,14 +1992,11 @@
           <t>69</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_35</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Domain Layer (Models)</t>
@@ -2058,13 +2021,11 @@
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M05_AU19</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2105,14 +2066,11 @@
           <t>69</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_33</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Business Logic Layer (Services)</t>
@@ -2136,13 +2094,11 @@
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M05_AU18</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2183,14 +2139,11 @@
           <t>81</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_55</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Kubernetes</t>
@@ -2217,13 +2170,11 @@
           <t>CF_M05_AU07</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M05_AU35</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2264,7 +2215,6 @@
           <t>68</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
@@ -2275,7 +2225,6 @@
           <t>P_05</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Layered Architecture</t>
@@ -2297,14 +2246,11 @@
       <c r="P15" t="n">
         <v>68.69</v>
       </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2345,14 +2291,11 @@
           <t>84</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_60</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>SonarQube</t>
@@ -2379,13 +2322,11 @@
           <t>CF_M05_AU32</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M05_AU08</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2426,7 +2367,6 @@
           <t>60</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
@@ -2437,7 +2377,6 @@
           <t>P_02</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Cloud Architecture</t>
@@ -2457,14 +2396,11 @@
       <c r="P17" t="n">
         <v>60</v>
       </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M05_P05</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2505,14 +2441,11 @@
           <t>60</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>AU_22</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>GSB</t>
@@ -2537,13 +2470,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M05_AU12</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2589,13 +2520,11 @@
           <t>['AU_64']</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>AU_26</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>HTTP</t>
@@ -2620,13 +2549,11 @@
           <t>CF_M05_AU34</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M05_AU31</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2667,14 +2594,11 @@
           <t>62</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>AU_28</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>View</t>
@@ -2700,13 +2624,11 @@
           <t>CF_M05_P03</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M05_AU13</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2747,14 +2669,11 @@
           <t>81</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>AU_56</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Docker</t>
@@ -2778,13 +2697,11 @@
           <t>CF_M05_AU32</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M05_AU33</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2825,14 +2742,11 @@
           <t>60</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>AU_21</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Ordering</t>
@@ -2859,13 +2773,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>CF_M05_AU11</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2906,14 +2818,11 @@
           <t>81</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>AU_54</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Amazon EKS</t>
@@ -2939,13 +2848,11 @@
           <t>CF_M05_P05</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>CF_M05_AU07</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2986,14 +2893,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>AU_25</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Spring Boot</t>
@@ -3019,13 +2923,11 @@
           <t>CF_M05_AU32</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>CF_M05_AU29</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3066,7 +2968,6 @@
           <t>62</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
@@ -3077,7 +2978,6 @@
           <t>P_04</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>MVVM</t>
@@ -3097,14 +2997,11 @@
       <c r="P25" t="n">
         <v>62</v>
       </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>CF_M05_P03</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3145,14 +3042,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>AU_24</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Angular</t>
@@ -3176,13 +3070,11 @@
           <t>CF_M05_AU06</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>CF_M05_AU30</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3223,7 +3115,6 @@
           <t>56</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
@@ -3234,7 +3125,6 @@
           <t>P_01</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Microservices</t>
@@ -3253,14 +3143,11 @@
       <c r="P27" t="n">
         <v>56</v>
       </c>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3301,7 +3188,6 @@
           <t>61</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
@@ -3312,7 +3198,6 @@
           <t>P_03</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>Client-Server</t>
@@ -3333,7 +3218,6 @@
       <c r="P28" t="n">
         <v>61</v>
       </c>
-      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
           <t>Design Pattern</t>
@@ -3344,7 +3228,6 @@
           <t>CF_M05_P02</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3385,14 +3268,11 @@
           <t>64</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>AU_29</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>ViewModel</t>
@@ -3418,13 +3298,11 @@
           <t>CF_M05_P03</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>CF_M05_AU14</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3465,14 +3343,11 @@
           <t>87</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>AU_62</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>Grafana</t>
@@ -3496,13 +3371,11 @@
           <t>CF_M05_AU32</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>CF_M05_AU09</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3576,7 +3449,6 @@
           <t>Volkswagen Group Services (VWGS)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Volkswagen Group Services forms part of the Volkswagen Group, a German multinational automotive manufacturing group and one of the world's largest automobile manufacturers, and exists to exclusively support the group's different companies globally.</t>
@@ -3612,7 +3484,6 @@
           <t>Commercial IT Services</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>This project is developed within the Commercial IT Services department, which is dedicated to supporting and providing IT solutions for projects related to commercial processes.</t>
@@ -3648,7 +3519,6 @@
           <t>NADIN</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>A program called NADIN was created that manages a global change in the architecture of all applications within its market.</t>
@@ -3684,7 +3554,6 @@
           <t>Integration Bus</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>A demand arises for a solution that acts as an integration bus allowing interoperability between systems, process standardization, and the agile incorporation of new functionalities within the English market with NADIN.</t>
@@ -3720,7 +3589,6 @@
           <t>NiX UK</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>This solution is named NiX UK and is developed in Spain as a cloud-based service layer that provides solutions and applications aimed at the group's importers according to business needs.</t>
@@ -3756,7 +3624,6 @@
           <t>NiX MED</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>At a certain point, in parallel, the development of a very similar solution for the Mediterranean market called NiX MED began.</t>
@@ -3792,7 +3659,6 @@
           <t>Personal or desktop device</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Technology cloud: Model of storage and management of computing resources through the Internet that allows accessing, processing, and hosting data or applications remotely.</t>
@@ -3828,7 +3694,6 @@
           <t>Volkswagen Group</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>This project, although it has as possible clients all the brands that form part of the Volkswagen group, will focus on two clients: SEAT and VGED.</t>
@@ -3864,7 +3729,6 @@
           <t>SEAT</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>This project, although it has as possible clients all the brands that form part of the Volkswagen group, will focus on two clients: SEAT and VGED.</t>
@@ -3900,7 +3764,6 @@
           <t>VGED</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>This latter encompasses the brands of AUDI, SKODA, and VOLKSWAGEN.</t>
@@ -3936,7 +3799,6 @@
           <t>AUDI</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>This latter encompasses the brands of AUDI, SKODA, and VOLKSWAGEN.</t>
@@ -3972,7 +3834,6 @@
           <t>SKODA</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>This latter encompasses the brands of AUDI, SKODA, and VOLKSWAGEN.</t>
@@ -4008,7 +3869,6 @@
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>This latter encompasses the brands of AUDI, SKODA, and VOLKSWAGEN.</t>
@@ -4044,7 +3904,6 @@
           <t>Commercial Cloud Data Management Application</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>The user accesses the data management application Commercial Cloud.</t>
@@ -4080,7 +3939,6 @@
           <t>frontEnd</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>This component incorporates the binaries necessary for the frontEnd both of the portal itself and of the rest of the portal's applications.</t>
@@ -4116,7 +3974,6 @@
           <t>Amazon Web Services</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>The provider for this project is Amazon Web Services which has a broad catalog of cloud services and resources.</t>
@@ -4152,7 +4009,6 @@
           <t>JSON</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>The message exchange protocol used in this case is HTTP and the data format employed is JSON.</t>
@@ -4188,7 +4044,6 @@
           <t>Models</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>To finish, Models are the TypeScript classes that define the data contract consumed by the view and by the ViewModel.</t>
@@ -4224,7 +4079,6 @@
           <t>Angular CLI</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>The construction and execution of all the frontEnd is carried out using Angular CLI which generates an optimized and minimized version of the application.</t>
@@ -4260,7 +4114,6 @@
           <t>Controllers</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Within each microservice there is a Controller class for each model.</t>
@@ -4296,7 +4149,6 @@
           <t>Services</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Services offer the interface and implementation of all the business logic of the application.</t>
@@ -4332,7 +4184,6 @@
           <t>Models</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>Models represent the internal and persistent structure of the system's entities identically reflecting the stored information.</t>
@@ -4368,7 +4219,6 @@
           <t>DTOs</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>Data Transfer Objects (DTOs) act as information containers that allow structuring the data necessary for each request, providing a customized format depending on response requirements.</t>
@@ -4404,7 +4254,6 @@
           <t>Mappers</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>Mappers are responsible for the conversion between DTOs and models.</t>
@@ -4440,7 +4289,6 @@
           <t>Repositories</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>Finally, Repositories are responsible for executing queries on the database.</t>
@@ -4476,7 +4324,6 @@
           <t>Angular 11+</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>Angular is a web development framework created by Google, based on the programming language superset of JavaScript called TypeScript, which allows building modern single-page applications (SPA).</t>
@@ -4512,7 +4359,6 @@
           <t>TypeScript</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>Angular is a web development framework created by Google, based on the programming language superset of JavaScript called TypeScript...</t>
@@ -4548,7 +4394,6 @@
           <t>Spring Data</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>Spring Data is a Spring project that simplifies data access and management in Java applications...</t>
@@ -4584,7 +4429,6 @@
           <t>JPA 2.2</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>...while JPA (Java Persistence API) is a specification that defines how to map Java objects to relational databases.</t>
@@ -4620,7 +4464,6 @@
           <t>Spring</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>Spring Data is a Spring project that simplifies data access and management in Java applications...</t>
@@ -4656,7 +4499,6 @@
           <t>Java</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>This combination is used to manage data persistence, which allows interacting with databases in a simpler and object-oriented way.</t>
@@ -4692,7 +4534,6 @@
           <t>Spring Boot 2.2.2</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>Spring Boot is a framework that simplifies the creation of Spring-based Java applications, offering automatic configuration and tools that allow deploying applications quickly.</t>
@@ -4728,7 +4569,6 @@
           <t>Java OpenJDK 17</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>OpenJDK is a free and open implementation of the Java Development Kit (JDK), the platform for developing and running Java applications.</t>
@@ -4764,7 +4604,6 @@
           <t>Gitflow</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>The management of each repository is done through Gitflow.</t>
@@ -4800,7 +4639,6 @@
           <t>IntelliJ IDEA</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>IntelliJ IDEA is an integrated development environment (IDE) created by JetBrains, designed primarily for software development in Java...</t>
@@ -4836,7 +4674,6 @@
           <t>Visual Studio Code (VS Code)</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>Visual Studio Code is a lightweight, cross-platform, free source code editor developed by Microsoft...</t>
@@ -4872,7 +4709,6 @@
           <t>Amazon ECR</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>These images are stored in Amazon ECR (Elastic Container Registry).</t>
@@ -4908,7 +4744,6 @@
           <t>JUnit 5</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>For unit tests, use has been made of the JUnit 5 and Mockito libraries.</t>
@@ -4944,7 +4779,6 @@
           <t>Mockito</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>For unit tests, use has been made of the JUnit 5 and Mockito libraries.</t>
@@ -4980,7 +4814,6 @@
           <t>Postman</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>For this task, use has been made of the Postman application to be able to test the modified calls given that there are no screens of the Ordering microservice in the application.</t>
@@ -5016,7 +4849,6 @@
           <t>Spring Boot Actuator</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>Spring Boot has native support for exposing metrics and application state information through the Spring Boot Actuator module which can then be visualized in Grafana.</t>
@@ -5047,7 +4879,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>presentation layer, business logic layer</t>
@@ -5083,7 +4914,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>business logic layer, data access layer</t>
@@ -5119,7 +4949,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>data access layer, domain layer</t>
@@ -5155,7 +4984,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>portal, frontend</t>
@@ -5191,7 +5019,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>angular 11+, frontend</t>
@@ -5227,7 +5054,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>portal, leader</t>
@@ -5263,7 +5089,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>portal, leader</t>
@@ -5279,7 +5104,6 @@
           <t>CF_M05_AU22</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
         <v>0.7506</v>
       </c>
@@ -5356,7 +5180,6 @@
           <t>Client (Frontend)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>The client, also called the frontEnd, is responsible for the presentation and user experience
@@ -5394,7 +5217,6 @@
           <t>Amazon RDS</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t xml:space="preserve"> the microservices are connected to a shared database (Amazon RDS) that is decoupled per
@@ -5431,7 +5253,6 @@
           <t>Model</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Models are the TypeScript classes that define the data contract consumed by the
@@ -5469,7 +5290,6 @@
           <t>Database</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
@@ -5502,7 +5322,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>communication log microservice, leader microservice, portal microservice, access control microservice, scheduler microservice, client (frontend), amazon eks</t>
@@ -5538,7 +5357,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>client (frontend), server (backend)</t>
@@ -5574,7 +5392,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>presentation layer (controllers), data access layer (repositories)</t>
@@ -5610,7 +5427,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>viewmodel, view, model</t>
@@ -5651,7 +5467,6 @@
           <t>REST</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t xml:space="preserve">Data access and logic management in this project is carried out through REST operations, which
@@ -5688,7 +5503,6 @@
           <t>Server (Backend)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
@@ -5720,7 +5534,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>viewmodel, server (backend)</t>
@@ -5761,7 +5574,6 @@
           <t>Shared Database</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
